--- a/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Mistral-Small-3.2-24B-Instruct-2506/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Mistral-Small-3.2-24B-Instruct-2506/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="D2">
         <v>282</v>
       </c>
       <c r="E2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G2">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D3">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="G3">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="H3">
         <v>426</v>
